--- a/471/food/2026-02-19-sm.xlsx
+++ b/471/food/2026-02-19-sm.xlsx
@@ -835,7 +835,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>МБОУ «Гудермесская СШ №1 им. Тимиралиева М.Х.»</t>
+          <t xml:space="preserve">МБОУ «Гудермесская СШ №1 им. Тимиралиева М.Х.» </t>
         </is>
       </c>
       <c r="C1" s="38" t="n"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>2026-02-19</t>
         </is>
       </c>
     </row>
